--- a/repository_snapshot_portfolio_value_aandelen.xlsx
+++ b/repository_snapshot_portfolio_value_aandelen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\python_coding\portefeuille_viewer\portefeuille_viewer_experiment_0.13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177B883D-7383-4853-A739-7081FDF2448F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E5053C-2F72-4F7E-B9B3-FB6791987CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="-110" windowWidth="37130" windowHeight="21820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2671,7 +2671,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H144"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2708,7 +2707,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2734,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2812,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2864,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2890,7 +2889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2916,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2942,7 +2941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -2968,7 +2967,7 @@
         <v>18532.2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2994,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -3020,7 +3019,7 @@
         <v>4658</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -3046,7 +3045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -3072,7 +3071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -3124,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>93.81</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>8097</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -3202,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -3280,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -3306,7 +3305,7 @@
         <v>12024</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -3358,7 +3357,7 @@
         <v>18175</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -3384,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -3436,7 +3435,7 @@
         <v>131.16</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -3462,7 +3461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -3488,7 +3487,7 @@
         <v>15636.12</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -3514,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -3540,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -3618,7 +3617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -3644,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>24</v>
       </c>
@@ -3670,7 +3669,7 @@
         <v>114.84</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -3696,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -3722,7 +3721,7 @@
         <v>18812</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>24</v>
       </c>
@@ -3774,7 +3773,7 @@
         <v>41377.300000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -3852,7 +3851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>19</v>
       </c>
@@ -3878,7 +3877,7 @@
         <v>5609.54</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>24</v>
       </c>
@@ -3904,7 +3903,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -3930,7 +3929,7 @@
         <v>17727.5</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -3956,7 +3955,7 @@
         <v>292.82</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>19</v>
       </c>
@@ -3982,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -4008,7 +4007,7 @@
         <v>3993</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>19</v>
       </c>
@@ -4034,7 +4033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>24</v>
       </c>
@@ -4060,7 +4059,7 @@
         <v>11736.8</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>16</v>
       </c>
@@ -4086,7 +4085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -4112,7 +4111,7 @@
         <v>15499</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -4164,7 +4163,7 @@
         <v>13981.4</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -4190,7 +4189,7 @@
         <v>8906</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -4216,7 +4215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -4242,7 +4241,7 @@
         <v>11976</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -4268,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>16</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -4320,7 +4319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -4346,7 +4345,7 @@
         <v>591.4</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -4372,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -4398,7 +4397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>16</v>
       </c>
@@ -4424,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -4450,7 +4449,7 @@
         <v>5734</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -4476,7 +4475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -4528,7 +4527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>16</v>
       </c>
@@ -4580,7 +4579,7 @@
         <v>1450.9</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -4606,7 +4605,7 @@
         <v>51604</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>8</v>
       </c>
@@ -4632,7 +4631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>8</v>
       </c>
@@ -4658,7 +4657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>8</v>
       </c>
@@ -4684,7 +4683,7 @@
         <v>11186</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -4762,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>19</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -4814,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>8</v>
       </c>
@@ -4840,7 +4839,7 @@
         <v>13974</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -4866,7 +4865,7 @@
         <v>205.78</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>19</v>
       </c>
@@ -4892,7 +4891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>8</v>
       </c>
@@ -4918,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -4944,7 +4943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>8</v>
       </c>
@@ -4970,7 +4969,7 @@
         <v>7993.0000000000009</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>16</v>
       </c>
@@ -4996,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>24</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>185.72</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>24</v>
       </c>
@@ -5048,7 +5047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -5100,7 +5099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>24</v>
       </c>
@@ -5126,7 +5125,7 @@
         <v>208.68</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -5152,7 +5151,7 @@
         <v>33558</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -5178,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -5204,7 +5203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>24</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -5282,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -5308,7 +5307,7 @@
         <v>10636.5</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -5334,7 +5333,7 @@
         <v>327.9</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>8</v>
       </c>
@@ -5360,7 +5359,7 @@
         <v>16194</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -5386,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -5412,7 +5411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -5438,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -5464,7 +5463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -5490,7 +5489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>24</v>
       </c>
@@ -5516,7 +5515,7 @@
         <v>527.20000000000005</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -5542,7 +5541,7 @@
         <v>6510</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -5568,7 +5567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>24</v>
       </c>
@@ -5594,7 +5593,7 @@
         <v>118.56</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -5620,7 +5619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -5646,7 +5645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -5672,7 +5671,7 @@
         <v>8906</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -5724,7 +5723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>19</v>
       </c>
@@ -5750,7 +5749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>19</v>
       </c>
@@ -5776,7 +5775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -5802,7 +5801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>19</v>
       </c>
@@ -5828,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>8</v>
       </c>
@@ -5854,7 +5853,7 @@
         <v>-2218.8000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -5880,7 +5879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>19</v>
       </c>
@@ -5906,7 +5905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>8</v>
       </c>
@@ -5932,7 +5931,7 @@
         <v>14318</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -5958,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -5984,7 +5983,7 @@
         <v>229.56</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -6062,7 +6061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>24</v>
       </c>
@@ -6088,7 +6087,7 @@
         <v>424.9</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -6114,7 +6113,7 @@
         <v>9341</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -6140,7 +6139,7 @@
         <v>4689.3</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -6166,7 +6165,7 @@
         <v>10538.34</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>8</v>
       </c>
@@ -6192,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -6218,7 +6217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -6244,7 +6243,7 @@
         <v>14477</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -6270,7 +6269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -6296,7 +6295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -6322,7 +6321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -6348,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -6374,7 +6373,7 @@
         <v>9341</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -6400,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -6427,13 +6426,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H144" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Inf Tech"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H144" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>